--- a/KatalonData/IWPBootstrapData/NormalizedSharedData.xlsx
+++ b/KatalonData/IWPBootstrapData/NormalizedSharedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E946AF49-BF29-47B3-90B0-C11279E9AE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D67B163-758A-4458-9F6F-0DAE40A8F6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1956" yWindow="1404" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="5" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
   </bookViews>
   <sheets>
     <sheet name="NameData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t>65987541</t>
-  </si>
-  <si>
-    <t>65239412</t>
   </si>
   <si>
     <t>25 main st</t>
@@ -726,7 +723,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -769,7 +766,7 @@
         <v>55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -777,7 +774,7 @@
         <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -940,22 +937,22 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -988,13 +985,13 @@
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1014,7 +1011,7 @@
         <v>52</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1025,7 +1022,7 @@
         <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>56</v>
@@ -1034,7 +1031,7 @@
         <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1051,10 +1048,10 @@
         <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,10 +1103,10 @@
         <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1117,13 +1114,13 @@
         <v>52</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1163,10 +1160,10 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1174,7 +1171,7 @@
         <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1187,7 +1184,7 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1243,16 +1240,16 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1265,10 +1262,10 @@
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
